--- a/survey_templates/043_health_challenges_survey--survey_templates.xlsx
+++ b/survey_templates/043_health_challenges_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'1-3_hours'}</t>
+          <t>1-3_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '1-3 hours'}</t>
+          <t>1-3 hours</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'4-6_hours'}</t>
+          <t>4-6_hours</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '4-6 hours'}</t>
+          <t>4-6 hours</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'7-9_hours'}</t>
+          <t>7-9_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '7-9 hours'}</t>
+          <t>7-9 hours</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'10+_hours'}</t>
+          <t>10+_hours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '10+ hours'}</t>
+          <t>10+ hours</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_3_hours'}</t>
+          <t>less_than_3_hours</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Less than 3 hours'}</t>
+          <t>Less than 3 hours</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'some'}</t>
+          <t>some</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Some'}</t>
+          <t>Some</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'a_lot'}</t>
+          <t>a_lot</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'A lot'}</t>
+          <t>A lot</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'partner'}</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Partner'}</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'chronic_condition'}</t>
+          <t>chronic_condition</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Chronic Condition'}</t>
+          <t>Chronic Condition</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'acute_condition'}</t>
+          <t>acute_condition</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Acute Condition'}</t>
+          <t>Acute Condition</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'physical_activity'}</t>
+          <t>physical_activity</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Activity'}</t>
+          <t>Physical Activity</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'mental_health'}</t>
+          <t>mental_health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Mental Health'}</t>
+          <t>Mental Health</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'nutrition'}</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Nutrition'}</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'sleep'}</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Sleep'}</t>
+          <t>Sleep</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'physical_activity'}</t>
+          <t>physical_activity</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Activity'}</t>
+          <t>Physical Activity</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'mental_health'}</t>
+          <t>mental_health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Mental Health'}</t>
+          <t>Mental Health</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'nutrition'}</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Nutrition'}</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'sleep'}</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Sleep'}</t>
+          <t>Sleep</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'physical_activity'}</t>
+          <t>physical_activity</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Activity'}</t>
+          <t>Physical Activity</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'mental_health'}</t>
+          <t>mental_health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Mental Health'}</t>
+          <t>Mental Health</t>
         </is>
       </c>
     </row>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'nutrition'}</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Nutrition'}</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'sleep'}</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Sleep'}</t>
+          <t>Sleep</t>
         </is>
       </c>
     </row>
@@ -1951,12 +1951,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'physical_activity'}</t>
+          <t>physical_activity</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Activity'}</t>
+          <t>Physical Activity</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'mental_health'}</t>
+          <t>mental_health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'Mental Health'}</t>
+          <t>Mental Health</t>
         </is>
       </c>
     </row>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'nutrition'}</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'Nutrition'}</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'sleep'}</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'Sleep'}</t>
+          <t>Sleep</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'physical_activity'}</t>
+          <t>physical_activity</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Activity'}</t>
+          <t>Physical Activity</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'mental_health'}</t>
+          <t>mental_health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'Mental Health'}</t>
+          <t>Mental Health</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'nutrition'}</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'Nutrition'}</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_'sleep'}</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 'Sleep'}</t>
+          <t>Sleep</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_'physical_activity'}</t>
+          <t>physical_activity</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Activity'}</t>
+          <t>Physical Activity</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_'mental_health'}</t>
+          <t>mental_health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 'Mental Health'}</t>
+          <t>Mental Health</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_'nutrition'}</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 'Nutrition'}</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_'sleep'}</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 'Sleep'}</t>
+          <t>Sleep</t>
         </is>
       </c>
     </row>
